--- a/DATA/COMODITIES.xlsx
+++ b/DATA/COMODITIES.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2766"/>
+  <dimension ref="A1:F2902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55747,6 +55747,2726 @@
         <v>77.37400054931641</v>
       </c>
     </row>
+    <row r="2767">
+      <c r="A2767" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B2767" t="n">
+        <v>4325.60009765625</v>
+      </c>
+      <c r="C2767" t="n">
+        <v>5.630000114440918</v>
+      </c>
+      <c r="D2767" t="n">
+        <v>1629.199951171875</v>
+      </c>
+      <c r="E2767" t="n">
+        <v>2034.5</v>
+      </c>
+      <c r="F2767" t="n">
+        <v>70.13400268554688</v>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B2768" t="n">
+        <v>4314.39990234375</v>
+      </c>
+      <c r="C2768" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="D2768" t="n">
+        <v>1668</v>
+      </c>
+      <c r="E2768" t="n">
+        <v>2125.699951171875</v>
+      </c>
+      <c r="F2768" t="n">
+        <v>70.55599975585938</v>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B2769" t="n">
+        <v>4436.89990234375</v>
+      </c>
+      <c r="C2769" t="n">
+        <v>5.924499988555908</v>
+      </c>
+      <c r="D2769" t="n">
+        <v>1742.199951171875</v>
+      </c>
+      <c r="E2769" t="n">
+        <v>2269.5</v>
+      </c>
+      <c r="F2769" t="n">
+        <v>76.16400146484375</v>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B2770" t="n">
+        <v>4482.2001953125</v>
+      </c>
+      <c r="C2770" t="n">
+        <v>6.010499954223633</v>
+      </c>
+      <c r="D2770" t="n">
+        <v>1865.599975585938</v>
+      </c>
+      <c r="E2770" t="n">
+        <v>2434</v>
+      </c>
+      <c r="F2770" t="n">
+        <v>80.52999877929688</v>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B2771" t="n">
+        <v>4449.2998046875</v>
+      </c>
+      <c r="C2771" t="n">
+        <v>5.809000015258789</v>
+      </c>
+      <c r="D2771" t="n">
+        <v>1767.199951171875</v>
+      </c>
+      <c r="E2771" t="n">
+        <v>2253.39990234375</v>
+      </c>
+      <c r="F2771" t="n">
+        <v>77.13500213623047</v>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B2772" t="n">
+        <v>4449.7001953125</v>
+      </c>
+      <c r="C2772" t="n">
+        <v>5.746500015258789</v>
+      </c>
+      <c r="D2772" t="n">
+        <v>1781.099975585938</v>
+      </c>
+      <c r="E2772" t="n">
+        <v>2251.699951171875</v>
+      </c>
+      <c r="F2772" t="n">
+        <v>74.71600341796875</v>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B2773" t="n">
+        <v>4490.2998046875</v>
+      </c>
+      <c r="C2773" t="n">
+        <v>5.855500221252441</v>
+      </c>
+      <c r="D2773" t="n">
+        <v>1853</v>
+      </c>
+      <c r="E2773" t="n">
+        <v>2278.300048828125</v>
+      </c>
+      <c r="F2773" t="n">
+        <v>78.88400268554688</v>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B2774" t="n">
+        <v>4604.2998046875</v>
+      </c>
+      <c r="C2774" t="n">
+        <v>5.985000133514404</v>
+      </c>
+      <c r="D2774" t="n">
+        <v>1921.300048828125</v>
+      </c>
+      <c r="E2774" t="n">
+        <v>2359.60009765625</v>
+      </c>
+      <c r="F2774" t="n">
+        <v>84.61000061035156</v>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B2775" t="n">
+        <v>4589.2001953125</v>
+      </c>
+      <c r="C2775" t="n">
+        <v>5.96999979019165</v>
+      </c>
+      <c r="D2775" t="n">
+        <v>1900.400024414062</v>
+      </c>
+      <c r="E2775" t="n">
+        <v>2333.800048828125</v>
+      </c>
+      <c r="F2775" t="n">
+        <v>85.87699890136719</v>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B2776" t="n">
+        <v>4626.2998046875</v>
+      </c>
+      <c r="C2776" t="n">
+        <v>6.008999824523926</v>
+      </c>
+      <c r="D2776" t="n">
+        <v>1886.900024414062</v>
+      </c>
+      <c r="E2776" t="n">
+        <v>2367.10009765625</v>
+      </c>
+      <c r="F2776" t="n">
+        <v>90.86900329589844</v>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B2777" t="n">
+        <v>4616.2998046875</v>
+      </c>
+      <c r="C2777" t="n">
+        <v>5.947999954223633</v>
+      </c>
+      <c r="D2777" t="n">
+        <v>1859</v>
+      </c>
+      <c r="E2777" t="n">
+        <v>2390</v>
+      </c>
+      <c r="F2777" t="n">
+        <v>91.87599945068359</v>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B2778" t="n">
+        <v>4588.39990234375</v>
+      </c>
+      <c r="C2778" t="n">
+        <v>5.78849983215332</v>
+      </c>
+      <c r="D2778" t="n">
+        <v>1805.199951171875</v>
+      </c>
+      <c r="E2778" t="n">
+        <v>2303.800048828125</v>
+      </c>
+      <c r="F2778" t="n">
+        <v>88.09100341796875</v>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B2779" t="n">
+        <v>4759.60009765625</v>
+      </c>
+      <c r="C2779" t="n">
+        <v>5.77299976348877</v>
+      </c>
+      <c r="D2779" t="n">
+        <v>1890.900024414062</v>
+      </c>
+      <c r="E2779" t="n">
+        <v>2431.5</v>
+      </c>
+      <c r="F2779" t="n">
+        <v>94.20600128173828</v>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B2780" t="n">
+        <v>4831.7998046875</v>
+      </c>
+      <c r="C2780" t="n">
+        <v>5.729499816894531</v>
+      </c>
+      <c r="D2780" t="n">
+        <v>1865.199951171875</v>
+      </c>
+      <c r="E2780" t="n">
+        <v>2480.39990234375</v>
+      </c>
+      <c r="F2780" t="n">
+        <v>92.20999908447266</v>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2781" t="n">
+        <v>4908.7998046875</v>
+      </c>
+      <c r="C2781" t="n">
+        <v>5.742499828338623</v>
+      </c>
+      <c r="D2781" t="n">
+        <v>1910.300048828125</v>
+      </c>
+      <c r="E2781" t="n">
+        <v>2561.800048828125</v>
+      </c>
+      <c r="F2781" t="n">
+        <v>95.97599792480469</v>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B2782" t="n">
+        <v>4976.2001953125</v>
+      </c>
+      <c r="C2782" t="n">
+        <v>5.910999774932861</v>
+      </c>
+      <c r="D2782" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E2782" t="n">
+        <v>2722.10009765625</v>
+      </c>
+      <c r="F2782" t="n">
+        <v>100.9250030517578</v>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B2783" t="n">
+        <v>5079.7001953125</v>
+      </c>
+      <c r="C2783" t="n">
+        <v>5.984000205993652</v>
+      </c>
+      <c r="D2783" t="n">
+        <v>2169.89990234375</v>
+      </c>
+      <c r="E2783" t="n">
+        <v>2852.39990234375</v>
+      </c>
+      <c r="F2783" t="n">
+        <v>115.0800018310547</v>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B2784" t="n">
+        <v>5079.89990234375</v>
+      </c>
+      <c r="C2784" t="n">
+        <v>5.828499794006348</v>
+      </c>
+      <c r="D2784" t="n">
+        <v>1861.800048828125</v>
+      </c>
+      <c r="E2784" t="n">
+        <v>2513.199951171875</v>
+      </c>
+      <c r="F2784" t="n">
+        <v>105.5230026245117</v>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B2785" t="n">
+        <v>5301.60009765625</v>
+      </c>
+      <c r="C2785" t="n">
+        <v>5.892499923706055</v>
+      </c>
+      <c r="D2785" t="n">
+        <v>2025.400024414062</v>
+      </c>
+      <c r="E2785" t="n">
+        <v>2605.699951171875</v>
+      </c>
+      <c r="F2785" t="n">
+        <v>113.1110000610352</v>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B2786" t="n">
+        <v>5318.39990234375</v>
+      </c>
+      <c r="C2786" t="n">
+        <v>6.17549991607666</v>
+      </c>
+      <c r="D2786" t="n">
+        <v>2000.599975585938</v>
+      </c>
+      <c r="E2786" t="n">
+        <v>2597.39990234375</v>
+      </c>
+      <c r="F2786" t="n">
+        <v>114.0370025634766</v>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B2787" t="n">
+        <v>4713.89990234375</v>
+      </c>
+      <c r="C2787" t="n">
+        <v>5.896999835968018</v>
+      </c>
+      <c r="D2787" t="n">
+        <v>1688.300048828125</v>
+      </c>
+      <c r="E2787" t="n">
+        <v>2102.800048828125</v>
+      </c>
+      <c r="F2787" t="n">
+        <v>78.29000091552734</v>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B2788" t="n">
+        <v>4622.5</v>
+      </c>
+      <c r="C2788" t="n">
+        <v>5.801499843597412</v>
+      </c>
+      <c r="D2788" t="n">
+        <v>1689.900024414062</v>
+      </c>
+      <c r="E2788" t="n">
+        <v>2093.5</v>
+      </c>
+      <c r="F2788" t="n">
+        <v>76.77799987792969</v>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B2789" t="n">
+        <v>4903.7001953125</v>
+      </c>
+      <c r="C2789" t="n">
+        <v>6.0625</v>
+      </c>
+      <c r="D2789" t="n">
+        <v>1746.099975585938</v>
+      </c>
+      <c r="E2789" t="n">
+        <v>2195.60009765625</v>
+      </c>
+      <c r="F2789" t="n">
+        <v>83.04199981689453</v>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B2790" t="n">
+        <v>4920.39990234375</v>
+      </c>
+      <c r="C2790" t="n">
+        <v>5.826000213623047</v>
+      </c>
+      <c r="D2790" t="n">
+        <v>1726.199951171875</v>
+      </c>
+      <c r="E2790" t="n">
+        <v>2162.699951171875</v>
+      </c>
+      <c r="F2790" t="n">
+        <v>84.16500091552734</v>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B2791" t="n">
+        <v>4861.39990234375</v>
+      </c>
+      <c r="C2791" t="n">
+        <v>5.798999786376953</v>
+      </c>
+      <c r="D2791" t="n">
+        <v>1688.900024414062</v>
+      </c>
+      <c r="E2791" t="n">
+        <v>2061.60009765625</v>
+      </c>
+      <c r="F2791" t="n">
+        <v>76.52899932861328</v>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B2792" t="n">
+        <v>4951.2001953125</v>
+      </c>
+      <c r="C2792" t="n">
+        <v>5.863500118255615</v>
+      </c>
+      <c r="D2792" t="n">
+        <v>1732.699951171875</v>
+      </c>
+      <c r="E2792" t="n">
+        <v>2093.300048828125</v>
+      </c>
+      <c r="F2792" t="n">
+        <v>76.73500061035156</v>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B2793" t="n">
+        <v>5050.89990234375</v>
+      </c>
+      <c r="C2793" t="n">
+        <v>5.945000171661377</v>
+      </c>
+      <c r="D2793" t="n">
+        <v>1737.099975585938</v>
+      </c>
+      <c r="E2793" t="n">
+        <v>2108.89990234375</v>
+      </c>
+      <c r="F2793" t="n">
+        <v>82.06500244140625</v>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B2794" t="n">
+        <v>5003.7998046875</v>
+      </c>
+      <c r="C2794" t="n">
+        <v>5.895999908447266</v>
+      </c>
+      <c r="D2794" t="n">
+        <v>1722.699951171875</v>
+      </c>
+      <c r="E2794" t="n">
+        <v>2091.60009765625</v>
+      </c>
+      <c r="F2794" t="n">
+        <v>80.21800231933594</v>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B2795" t="n">
+        <v>5071.60009765625</v>
+      </c>
+      <c r="C2795" t="n">
+        <v>5.948999881744385</v>
+      </c>
+      <c r="D2795" t="n">
+        <v>1735.300048828125</v>
+      </c>
+      <c r="E2795" t="n">
+        <v>2137.89990234375</v>
+      </c>
+      <c r="F2795" t="n">
+        <v>83.75399780273438</v>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B2796" t="n">
+        <v>4923.7001953125</v>
+      </c>
+      <c r="C2796" t="n">
+        <v>5.770999908447266</v>
+      </c>
+      <c r="D2796" t="n">
+        <v>1650.300048828125</v>
+      </c>
+      <c r="E2796" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F2796" t="n">
+        <v>75.54599761962891</v>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B2797" t="n">
+        <v>5022</v>
+      </c>
+      <c r="C2797" t="n">
+        <v>5.792500019073486</v>
+      </c>
+      <c r="D2797" t="n">
+        <v>1697.5</v>
+      </c>
+      <c r="E2797" t="n">
+        <v>2071.199951171875</v>
+      </c>
+      <c r="F2797" t="n">
+        <v>77.85099792480469</v>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B2798" t="n">
+        <v>4882.89990234375</v>
+      </c>
+      <c r="C2798" t="n">
+        <v>5.632999897003174</v>
+      </c>
+      <c r="D2798" t="n">
+        <v>1675.199951171875</v>
+      </c>
+      <c r="E2798" t="n">
+        <v>2012.5</v>
+      </c>
+      <c r="F2798" t="n">
+        <v>73.44699859619141</v>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B2799" t="n">
+        <v>4986.5</v>
+      </c>
+      <c r="C2799" t="n">
+        <v>5.793499946594238</v>
+      </c>
+      <c r="D2799" t="n">
+        <v>1751.300048828125</v>
+      </c>
+      <c r="E2799" t="n">
+        <v>2106.39990234375</v>
+      </c>
+      <c r="F2799" t="n">
+        <v>77.50900268554688</v>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B2800" t="n">
+        <v>4975.89990234375</v>
+      </c>
+      <c r="C2800" t="n">
+        <v>5.730000019073486</v>
+      </c>
+      <c r="D2800" t="n">
+        <v>1690.400024414062</v>
+      </c>
+      <c r="E2800" t="n">
+        <v>2062.300048828125</v>
+      </c>
+      <c r="F2800" t="n">
+        <v>77.56500244140625</v>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B2801" t="n">
+        <v>5059.2998046875</v>
+      </c>
+      <c r="C2801" t="n">
+        <v>5.830999851226807</v>
+      </c>
+      <c r="D2801" t="n">
+        <v>1774.199951171875</v>
+      </c>
+      <c r="E2801" t="n">
+        <v>2169.699951171875</v>
+      </c>
+      <c r="F2801" t="n">
+        <v>82.28299713134766</v>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B2802" t="n">
+        <v>5204.7001953125</v>
+      </c>
+      <c r="C2802" t="n">
+        <v>5.77299976348877</v>
+      </c>
+      <c r="D2802" t="n">
+        <v>1772.199951171875</v>
+      </c>
+      <c r="E2802" t="n">
+        <v>2146.39990234375</v>
+      </c>
+      <c r="F2802" t="n">
+        <v>86.52300262451172</v>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B2803" t="n">
+        <v>5155.7998046875</v>
+      </c>
+      <c r="C2803" t="n">
+        <v>5.922999858856201</v>
+      </c>
+      <c r="D2803" t="n">
+        <v>1813.5</v>
+      </c>
+      <c r="E2803" t="n">
+        <v>2181.10009765625</v>
+      </c>
+      <c r="F2803" t="n">
+        <v>87.45700073242188</v>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B2804" t="n">
+        <v>5206.39990234375</v>
+      </c>
+      <c r="C2804" t="n">
+        <v>5.979499816894531</v>
+      </c>
+      <c r="D2804" t="n">
+        <v>1834.099975585938</v>
+      </c>
+      <c r="E2804" t="n">
+        <v>2325.60009765625</v>
+      </c>
+      <c r="F2804" t="n">
+        <v>90.93900299072266</v>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B2805" t="n">
+        <v>5176.5</v>
+      </c>
+      <c r="C2805" t="n">
+        <v>5.947000026702881</v>
+      </c>
+      <c r="D2805" t="n">
+        <v>1748.599975585938</v>
+      </c>
+      <c r="E2805" t="n">
+        <v>2230.699951171875</v>
+      </c>
+      <c r="F2805" t="n">
+        <v>86.99800109863281</v>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B2806" t="n">
+        <v>5230.5</v>
+      </c>
+      <c r="C2806" t="n">
+        <v>6.004499912261963</v>
+      </c>
+      <c r="D2806" t="n">
+        <v>1792.199951171875</v>
+      </c>
+      <c r="E2806" t="n">
+        <v>2365.60009765625</v>
+      </c>
+      <c r="F2806" t="n">
+        <v>92.68199920654297</v>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2807" t="n">
+        <v>5294.39990234375</v>
+      </c>
+      <c r="C2807" t="n">
+        <v>5.894499778747559</v>
+      </c>
+      <c r="D2807" t="n">
+        <v>1762.599975585938</v>
+      </c>
+      <c r="E2807" t="n">
+        <v>2311.89990234375</v>
+      </c>
+      <c r="F2807" t="n">
+        <v>88.28399658203125</v>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B2808" t="n">
+        <v>5107.39990234375</v>
+      </c>
+      <c r="C2808" t="n">
+        <v>5.773499965667725</v>
+      </c>
+      <c r="D2808" t="n">
+        <v>1635</v>
+      </c>
+      <c r="E2808" t="n">
+        <v>2074.800048828125</v>
+      </c>
+      <c r="F2808" t="n">
+        <v>82.92299652099609</v>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B2809" t="n">
+        <v>5120.2001953125</v>
+      </c>
+      <c r="C2809" t="n">
+        <v>5.855000019073486</v>
+      </c>
+      <c r="D2809" t="n">
+        <v>1667.800048828125</v>
+      </c>
+      <c r="E2809" t="n">
+        <v>2154.699951171875</v>
+      </c>
+      <c r="F2809" t="n">
+        <v>82.63300323486328</v>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B2810" t="n">
+        <v>5065.2998046875</v>
+      </c>
+      <c r="C2810" t="n">
+        <v>5.752999782562256</v>
+      </c>
+      <c r="D2810" t="n">
+        <v>1620.199951171875</v>
+      </c>
+      <c r="E2810" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F2810" t="n">
+        <v>81.68699645996094</v>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="A2811" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B2811" t="n">
+        <v>5146.10009765625</v>
+      </c>
+      <c r="C2811" t="n">
+        <v>5.756999969482422</v>
+      </c>
+      <c r="D2811" t="n">
+        <v>1631.699951171875</v>
+      </c>
+      <c r="E2811" t="n">
+        <v>2142.39990234375</v>
+      </c>
+      <c r="F2811" t="n">
+        <v>83.81600189208984</v>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B2812" t="n">
+        <v>5091.5</v>
+      </c>
+      <c r="C2812" t="n">
+        <v>5.80049991607666</v>
+      </c>
+      <c r="D2812" t="n">
+        <v>1662.199951171875</v>
+      </c>
+      <c r="E2812" t="n">
+        <v>2169.60009765625</v>
+      </c>
+      <c r="F2812" t="n">
+        <v>84.03199768066406</v>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B2813" t="n">
+        <v>5229.7001953125</v>
+      </c>
+      <c r="C2813" t="n">
+        <v>5.903999805450439</v>
+      </c>
+      <c r="D2813" t="n">
+        <v>1668.699951171875</v>
+      </c>
+      <c r="E2813" t="n">
+        <v>2235</v>
+      </c>
+      <c r="F2813" t="n">
+        <v>89.08300018310547</v>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B2814" t="n">
+        <v>5167.39990234375</v>
+      </c>
+      <c r="C2814" t="n">
+        <v>5.845499992370605</v>
+      </c>
+      <c r="D2814" t="n">
+        <v>1624.400024414062</v>
+      </c>
+      <c r="E2814" t="n">
+        <v>2205</v>
+      </c>
+      <c r="F2814" t="n">
+        <v>85.06500244140625</v>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B2815" t="n">
+        <v>5115.7998046875</v>
+      </c>
+      <c r="C2815" t="n">
+        <v>5.82450008392334</v>
+      </c>
+      <c r="D2815" t="n">
+        <v>1621.900024414062</v>
+      </c>
+      <c r="E2815" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F2815" t="n">
+        <v>84.66999816894531</v>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B2816" t="n">
+        <v>5052.5</v>
+      </c>
+      <c r="C2816" t="n">
+        <v>5.714499950408936</v>
+      </c>
+      <c r="D2816" t="n">
+        <v>1554.099975585938</v>
+      </c>
+      <c r="E2816" t="n">
+        <v>2036.599975585938</v>
+      </c>
+      <c r="F2816" t="n">
+        <v>80.91400146484375</v>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B2817" t="n">
+        <v>4994</v>
+      </c>
+      <c r="C2817" t="n">
+        <v>5.790500164031982</v>
+      </c>
+      <c r="D2817" t="n">
+        <v>1584.5</v>
+      </c>
+      <c r="E2817" t="n">
+        <v>2089.5</v>
+      </c>
+      <c r="F2817" t="n">
+        <v>80.26300048828125</v>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B2818" t="n">
+        <v>5001</v>
+      </c>
+      <c r="C2818" t="n">
+        <v>5.726500034332275</v>
+      </c>
+      <c r="D2818" t="n">
+        <v>1614</v>
+      </c>
+      <c r="E2818" t="n">
+        <v>2131.800048828125</v>
+      </c>
+      <c r="F2818" t="n">
+        <v>79.52999877929688</v>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B2819" t="n">
+        <v>4889.89990234375</v>
+      </c>
+      <c r="C2819" t="n">
+        <v>5.553999900817871</v>
+      </c>
+      <c r="D2819" t="n">
+        <v>1517.099975585938</v>
+      </c>
+      <c r="E2819" t="n">
+        <v>2052</v>
+      </c>
+      <c r="F2819" t="n">
+        <v>77.23799896240234</v>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B2820" t="n">
+        <v>4600.7001953125</v>
+      </c>
+      <c r="C2820" t="n">
+        <v>5.433000087738037</v>
+      </c>
+      <c r="D2820" t="n">
+        <v>1434.599975585938</v>
+      </c>
+      <c r="E2820" t="n">
+        <v>1939.199951171875</v>
+      </c>
+      <c r="F2820" t="n">
+        <v>70.90200042724609</v>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B2821" t="n">
+        <v>4570.39990234375</v>
+      </c>
+      <c r="C2821" t="n">
+        <v>5.34250020980835</v>
+      </c>
+      <c r="D2821" t="n">
+        <v>1424.800048828125</v>
+      </c>
+      <c r="E2821" t="n">
+        <v>1970.599975585938</v>
+      </c>
+      <c r="F2821" t="n">
+        <v>69.36000061035156</v>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B2822" t="n">
+        <v>4404.10009765625</v>
+      </c>
+      <c r="C2822" t="n">
+        <v>5.439499855041504</v>
+      </c>
+      <c r="D2822" t="n">
+        <v>1411.300048828125</v>
+      </c>
+      <c r="E2822" t="n">
+        <v>1860.300048828125</v>
+      </c>
+      <c r="F2822" t="n">
+        <v>69.04900360107422</v>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B2823" t="n">
+        <v>4399.2998046875</v>
+      </c>
+      <c r="C2823" t="n">
+        <v>5.422500133514404</v>
+      </c>
+      <c r="D2823" t="n">
+        <v>1411.199951171875</v>
+      </c>
+      <c r="E2823" t="n">
+        <v>1892</v>
+      </c>
+      <c r="F2823" t="n">
+        <v>69.27400207519531</v>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B2824" t="n">
+        <v>4549.7998046875</v>
+      </c>
+      <c r="C2824" t="n">
+        <v>5.528999805450439</v>
+      </c>
+      <c r="D2824" t="n">
+        <v>1416</v>
+      </c>
+      <c r="E2824" t="n">
+        <v>1925.199951171875</v>
+      </c>
+      <c r="F2824" t="n">
+        <v>72.36100006103516</v>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B2825" t="n">
+        <v>4375.5</v>
+      </c>
+      <c r="C2825" t="n">
+        <v>5.446499824523926</v>
+      </c>
+      <c r="D2825" t="n">
+        <v>1341.300048828125</v>
+      </c>
+      <c r="E2825" t="n">
+        <v>1838.300048828125</v>
+      </c>
+      <c r="F2825" t="n">
+        <v>67.67099761962891</v>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B2826" t="n">
+        <v>4492</v>
+      </c>
+      <c r="C2826" t="n">
+        <v>5.467000007629395</v>
+      </c>
+      <c r="D2826" t="n">
+        <v>1390.900024414062</v>
+      </c>
+      <c r="E2826" t="n">
+        <v>1870.599975585938</v>
+      </c>
+      <c r="F2826" t="n">
+        <v>69.54499816894531</v>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2827" t="n">
+        <v>4526</v>
+      </c>
+      <c r="C2827" t="n">
+        <v>5.47599983215332</v>
+      </c>
+      <c r="D2827" t="n">
+        <v>1418</v>
+      </c>
+      <c r="E2827" t="n">
+        <v>1885.599975585938</v>
+      </c>
+      <c r="F2827" t="n">
+        <v>70.32399749755859</v>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B2828" t="n">
+        <v>4647.60009765625</v>
+      </c>
+      <c r="C2828" t="n">
+        <v>5.587500095367432</v>
+      </c>
+      <c r="D2828" t="n">
+        <v>1471.199951171875</v>
+      </c>
+      <c r="E2828" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F2828" t="n">
+        <v>74.69000244140625</v>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2829" t="n">
+        <v>4783.2001953125</v>
+      </c>
+      <c r="C2829" t="n">
+        <v>5.624000072479248</v>
+      </c>
+      <c r="D2829" t="n">
+        <v>1478.400024414062</v>
+      </c>
+      <c r="E2829" t="n">
+        <v>1969.300048828125</v>
+      </c>
+      <c r="F2829" t="n">
+        <v>75.86699676513672</v>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B2830" t="n">
+        <v>4651.5</v>
+      </c>
+      <c r="C2830" t="n">
+        <v>5.563000202178955</v>
+      </c>
+      <c r="D2830" t="n">
+        <v>1491.400024414062</v>
+      </c>
+      <c r="E2830" t="n">
+        <v>1963.800048828125</v>
+      </c>
+      <c r="F2830" t="n">
+        <v>72.73500061035156</v>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B2831" t="n">
+        <v>4656.7998046875</v>
+      </c>
+      <c r="C2831" t="n">
+        <v>5.583499908447266</v>
+      </c>
+      <c r="D2831" t="n">
+        <v>1476.199951171875</v>
+      </c>
+      <c r="E2831" t="n">
+        <v>1958.199951171875</v>
+      </c>
+      <c r="F2831" t="n">
+        <v>72.66100311279297</v>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B2832" t="n">
+        <v>4657.10009765625</v>
+      </c>
+      <c r="C2832" t="n">
+        <v>5.54449987411499</v>
+      </c>
+      <c r="D2832" t="n">
+        <v>1442</v>
+      </c>
+      <c r="E2832" t="n">
+        <v>1929.099975585938</v>
+      </c>
+      <c r="F2832" t="n">
+        <v>71.82599639892578</v>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B2833" t="n">
+        <v>4749.5</v>
+      </c>
+      <c r="C2833" t="n">
+        <v>5.759500026702881</v>
+      </c>
+      <c r="D2833" t="n">
+        <v>1586.900024414062</v>
+      </c>
+      <c r="E2833" t="n">
+        <v>2050.60009765625</v>
+      </c>
+      <c r="F2833" t="n">
+        <v>75.2239990234375</v>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B2834" t="n">
+        <v>4792.2001953125</v>
+      </c>
+      <c r="C2834" t="n">
+        <v>5.748000144958496</v>
+      </c>
+      <c r="D2834" t="n">
+        <v>1553</v>
+      </c>
+      <c r="E2834" t="n">
+        <v>2096.60009765625</v>
+      </c>
+      <c r="F2834" t="n">
+        <v>76.27700042724609</v>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B2835" t="n">
+        <v>4761.89990234375</v>
+      </c>
+      <c r="C2835" t="n">
+        <v>5.870500087738037</v>
+      </c>
+      <c r="D2835" t="n">
+        <v>1528.099975585938</v>
+      </c>
+      <c r="E2835" t="n">
+        <v>2049.10009765625</v>
+      </c>
+      <c r="F2835" t="n">
+        <v>76.32399749755859</v>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B2836" t="n">
+        <v>4742.39990234375</v>
+      </c>
+      <c r="C2836" t="n">
+        <v>5.97599983215332</v>
+      </c>
+      <c r="D2836" t="n">
+        <v>1569.800048828125</v>
+      </c>
+      <c r="E2836" t="n">
+        <v>2061.800048828125</v>
+      </c>
+      <c r="F2836" t="n">
+        <v>75.52300262451172</v>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B2837" t="n">
+        <v>4825</v>
+      </c>
+      <c r="C2837" t="n">
+        <v>6.070499897003174</v>
+      </c>
+      <c r="D2837" t="n">
+        <v>1579.400024414062</v>
+      </c>
+      <c r="E2837" t="n">
+        <v>2084.60009765625</v>
+      </c>
+      <c r="F2837" t="n">
+        <v>79.39099884033203</v>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B2838" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2838" t="n">
+        <v>6.072000026702881</v>
+      </c>
+      <c r="D2838" t="n">
+        <v>1578.099975585938</v>
+      </c>
+      <c r="E2838" t="n">
+        <v>2112.89990234375</v>
+      </c>
+      <c r="F2838" t="n">
+        <v>79.49099731445312</v>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B2839" t="n">
+        <v>4785.39990234375</v>
+      </c>
+      <c r="C2839" t="n">
+        <v>6.066500186920166</v>
+      </c>
+      <c r="D2839" t="n">
+        <v>1570.5</v>
+      </c>
+      <c r="E2839" t="n">
+        <v>2094.10009765625</v>
+      </c>
+      <c r="F2839" t="n">
+        <v>78.60600280761719</v>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B2840" t="n">
+        <v>4857.60009765625</v>
+      </c>
+      <c r="C2840" t="n">
+        <v>6.103499889373779</v>
+      </c>
+      <c r="D2840" t="n">
+        <v>1590.400024414062</v>
+      </c>
+      <c r="E2840" t="n">
+        <v>2124.5</v>
+      </c>
+      <c r="F2840" t="n">
+        <v>81.73799896240234</v>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B2841" t="n">
+        <v>4806.60009765625</v>
+      </c>
+      <c r="C2841" t="n">
+        <v>6.035999774932861</v>
+      </c>
+      <c r="D2841" t="n">
+        <v>1559.599975585938</v>
+      </c>
+      <c r="E2841" t="n">
+        <v>2070.699951171875</v>
+      </c>
+      <c r="F2841" t="n">
+        <v>79.95099639892578</v>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B2842" t="n">
+        <v>4698.39990234375</v>
+      </c>
+      <c r="C2842" t="n">
+        <v>6.001500129699707</v>
+      </c>
+      <c r="D2842" t="n">
+        <v>1531.699951171875</v>
+      </c>
+      <c r="E2842" t="n">
+        <v>2024.300048828125</v>
+      </c>
+      <c r="F2842" t="n">
+        <v>76.41100311279297</v>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B2843" t="n">
+        <v>4732.5</v>
+      </c>
+      <c r="C2843" t="n">
+        <v>6.119999885559082</v>
+      </c>
+      <c r="D2843" t="n">
+        <v>1547.099975585938</v>
+      </c>
+      <c r="E2843" t="n">
+        <v>2072.60009765625</v>
+      </c>
+      <c r="F2843" t="n">
+        <v>77.89299774169922</v>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B2844" t="n">
+        <v>4705.10009765625</v>
+      </c>
+      <c r="C2844" t="n">
+        <v>6.075500011444092</v>
+      </c>
+      <c r="D2844" t="n">
+        <v>1484.599975585938</v>
+      </c>
+      <c r="E2844" t="n">
+        <v>2022.599975585938</v>
+      </c>
+      <c r="F2844" t="n">
+        <v>75.46499633789062</v>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B2845" t="n">
+        <v>4722.2998046875</v>
+      </c>
+      <c r="C2845" t="n">
+        <v>6.023499965667725</v>
+      </c>
+      <c r="D2845" t="n">
+        <v>1501.5</v>
+      </c>
+      <c r="E2845" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F2845" t="n">
+        <v>76.38300323486328</v>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B2846" t="n">
+        <v>4675.39990234375</v>
+      </c>
+      <c r="C2846" t="n">
+        <v>6.01800012588501</v>
+      </c>
+      <c r="D2846" t="n">
+        <v>1477.699951171875</v>
+      </c>
+      <c r="E2846" t="n">
+        <v>1981.099975585938</v>
+      </c>
+      <c r="F2846" t="n">
+        <v>75.00299835205078</v>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B2847" t="n">
+        <v>4591.5</v>
+      </c>
+      <c r="C2847" t="n">
+        <v>5.91450023651123</v>
+      </c>
+      <c r="D2847" t="n">
+        <v>1461.099975585938</v>
+      </c>
+      <c r="E2847" t="n">
+        <v>1942.300048828125</v>
+      </c>
+      <c r="F2847" t="n">
+        <v>73.20500183105469</v>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B2848" t="n">
+        <v>4545.2001953125</v>
+      </c>
+      <c r="C2848" t="n">
+        <v>5.878499984741211</v>
+      </c>
+      <c r="D2848" t="n">
+        <v>1461.800048828125</v>
+      </c>
+      <c r="E2848" t="n">
+        <v>1885.300048828125</v>
+      </c>
+      <c r="F2848" t="n">
+        <v>71.56900024414062</v>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B2849" t="n">
+        <v>4614.7001953125</v>
+      </c>
+      <c r="C2849" t="n">
+        <v>5.926000118255615</v>
+      </c>
+      <c r="D2849" t="n">
+        <v>1526.400024414062</v>
+      </c>
+      <c r="E2849" t="n">
+        <v>1979</v>
+      </c>
+      <c r="F2849" t="n">
+        <v>73.53399658203125</v>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B2850" t="n">
+        <v>4629.89990234375</v>
+      </c>
+      <c r="C2850" t="n">
+        <v>5.932000160217285</v>
+      </c>
+      <c r="D2850" t="n">
+        <v>1539.199951171875</v>
+      </c>
+      <c r="E2850" t="n">
+        <v>1996.599975585938</v>
+      </c>
+      <c r="F2850" t="n">
+        <v>75.95099639892578</v>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B2851" t="n">
+        <v>4519.5</v>
+      </c>
+      <c r="C2851" t="n">
+        <v>5.795000076293945</v>
+      </c>
+      <c r="D2851" t="n">
+        <v>1474.699951171875</v>
+      </c>
+      <c r="E2851" t="n">
+        <v>1946.900024414062</v>
+      </c>
+      <c r="F2851" t="n">
+        <v>73.07199859619141</v>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="A2852" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B2852" t="n">
+        <v>4555.7998046875</v>
+      </c>
+      <c r="C2852" t="n">
+        <v>5.942999839782715</v>
+      </c>
+      <c r="D2852" t="n">
+        <v>1507.099975585938</v>
+      </c>
+      <c r="E2852" t="n">
+        <v>1960.699951171875</v>
+      </c>
+      <c r="F2852" t="n">
+        <v>73.10800170898438</v>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B2853" t="n">
+        <v>4681.89990234375</v>
+      </c>
+      <c r="C2853" t="n">
+        <v>6.136499881744385</v>
+      </c>
+      <c r="D2853" t="n">
+        <v>1546</v>
+      </c>
+      <c r="E2853" t="n">
+        <v>2048.699951171875</v>
+      </c>
+      <c r="F2853" t="n">
+        <v>76.81099700927734</v>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B2854" t="n">
+        <v>4699.7998046875</v>
+      </c>
+      <c r="C2854" t="n">
+        <v>6.127500057220459</v>
+      </c>
+      <c r="D2854" t="n">
+        <v>1517.800048828125</v>
+      </c>
+      <c r="E2854" t="n">
+        <v>2048.10009765625</v>
+      </c>
+      <c r="F2854" t="n">
+        <v>79.70099639892578</v>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B2855" t="n">
+        <v>4720.39990234375</v>
+      </c>
+      <c r="C2855" t="n">
+        <v>6.249000072479248</v>
+      </c>
+      <c r="D2855" t="n">
+        <v>1482.599975585938</v>
+      </c>
+      <c r="E2855" t="n">
+        <v>2047.199951171875</v>
+      </c>
+      <c r="F2855" t="n">
+        <v>80.39499664306641</v>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B2856" t="n">
+        <v>4718.7001953125</v>
+      </c>
+      <c r="C2856" t="n">
+        <v>6.41349983215332</v>
+      </c>
+      <c r="D2856" t="n">
+        <v>1513.800048828125</v>
+      </c>
+      <c r="E2856" t="n">
+        <v>2115.5</v>
+      </c>
+      <c r="F2856" t="n">
+        <v>85.48500061035156</v>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B2857" t="n">
+        <v>4677.60009765625</v>
+      </c>
+      <c r="C2857" t="n">
+        <v>6.485000133514404</v>
+      </c>
+      <c r="D2857" t="n">
+        <v>1485.699951171875</v>
+      </c>
+      <c r="E2857" t="n">
+        <v>2110</v>
+      </c>
+      <c r="F2857" t="n">
+        <v>85.12999725341797</v>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B2858" t="n">
+        <v>4697.7001953125</v>
+      </c>
+      <c r="C2858" t="n">
+        <v>6.635499954223633</v>
+      </c>
+      <c r="D2858" t="n">
+        <v>1531</v>
+      </c>
+      <c r="E2858" t="n">
+        <v>2187.10009765625</v>
+      </c>
+      <c r="F2858" t="n">
+        <v>88.88800048828125</v>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="A2859" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B2859" t="n">
+        <v>4678.10009765625</v>
+      </c>
+      <c r="C2859" t="n">
+        <v>6.567500114440918</v>
+      </c>
+      <c r="D2859" t="n">
+        <v>1456.599975585938</v>
+      </c>
+      <c r="E2859" t="n">
+        <v>2083.5</v>
+      </c>
+      <c r="F2859" t="n">
+        <v>84.91200256347656</v>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B2860" t="n">
+        <v>4555.7998046875</v>
+      </c>
+      <c r="C2860" t="n">
+        <v>6.251500129699707</v>
+      </c>
+      <c r="D2860" t="n">
+        <v>1422.900024414062</v>
+      </c>
+      <c r="E2860" t="n">
+        <v>1981.300048828125</v>
+      </c>
+      <c r="F2860" t="n">
+        <v>77.16100311279297</v>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B2861" t="n">
+        <v>4552.5</v>
+      </c>
+      <c r="C2861" t="n">
+        <v>6.271999835968018</v>
+      </c>
+      <c r="D2861" t="n">
+        <v>1417.800048828125</v>
+      </c>
+      <c r="E2861" t="n">
+        <v>1968.099975585938</v>
+      </c>
+      <c r="F2861" t="n">
+        <v>77.072998046875</v>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B2862" t="n">
+        <v>4506.2998046875</v>
+      </c>
+      <c r="C2862" t="n">
+        <v>6.164999961853027</v>
+      </c>
+      <c r="D2862" t="n">
+        <v>1360.199951171875</v>
+      </c>
+      <c r="E2862" t="n">
+        <v>1933.800048828125</v>
+      </c>
+      <c r="F2862" t="n">
+        <v>74.8280029296875</v>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B2863" t="n">
+        <v>4531.2998046875</v>
+      </c>
+      <c r="C2863" t="n">
+        <v>6.290500164031982</v>
+      </c>
+      <c r="D2863" t="n">
+        <v>1373.800048828125</v>
+      </c>
+      <c r="E2863" t="n">
+        <v>1949.800048828125</v>
+      </c>
+      <c r="F2863" t="n">
+        <v>75.85099792480469</v>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B2864" t="n">
+        <v>4539.7998046875</v>
+      </c>
+      <c r="C2864" t="n">
+        <v>6.256999969482422</v>
+      </c>
+      <c r="D2864" t="n">
+        <v>1383.400024414062</v>
+      </c>
+      <c r="E2864" t="n">
+        <v>1955.099975585938</v>
+      </c>
+      <c r="F2864" t="n">
+        <v>76.41400146484375</v>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B2865" t="n">
+        <v>4521</v>
+      </c>
+      <c r="C2865" t="n">
+        <v>6.342000007629395</v>
+      </c>
+      <c r="D2865" t="n">
+        <v>1358</v>
+      </c>
+      <c r="E2865" t="n">
+        <v>1931.599975585938</v>
+      </c>
+      <c r="F2865" t="n">
+        <v>75.89299774169922</v>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B2866" t="n">
+        <v>4500.39990234375</v>
+      </c>
+      <c r="C2866" t="n">
+        <v>6.361000061035156</v>
+      </c>
+      <c r="D2866" t="n">
+        <v>1385.800048828125</v>
+      </c>
+      <c r="E2866" t="n">
+        <v>1942.199951171875</v>
+      </c>
+      <c r="F2866" t="n">
+        <v>76.30500030517578</v>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B2867" t="n">
+        <v>4447.5</v>
+      </c>
+      <c r="C2867" t="n">
+        <v>6.304999828338623</v>
+      </c>
+      <c r="D2867" t="n">
+        <v>1395.599975585938</v>
+      </c>
+      <c r="E2867" t="n">
+        <v>1918.699951171875</v>
+      </c>
+      <c r="F2867" t="n">
+        <v>74.5989990234375</v>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B2868" t="n">
+        <v>4499.2998046875</v>
+      </c>
+      <c r="C2868" t="n">
+        <v>6.395999908447266</v>
+      </c>
+      <c r="D2868" t="n">
+        <v>1377.599975585938</v>
+      </c>
+      <c r="E2868" t="n">
+        <v>1921.599975585938</v>
+      </c>
+      <c r="F2868" t="n">
+        <v>75.64499664306641</v>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B2869" t="n">
+        <v>4560.5</v>
+      </c>
+      <c r="C2869" t="n">
+        <v>6.359499931335449</v>
+      </c>
+      <c r="D2869" t="n">
+        <v>1361</v>
+      </c>
+      <c r="E2869" t="n">
+        <v>1922.199951171875</v>
+      </c>
+      <c r="F2869" t="n">
+        <v>75.61599731445312</v>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B2870" t="n">
+        <v>4475.2001953125</v>
+      </c>
+      <c r="C2870" t="n">
+        <v>6.52400016784668</v>
+      </c>
+      <c r="D2870" t="n">
+        <v>1360.5</v>
+      </c>
+      <c r="E2870" t="n">
+        <v>1922.400024414062</v>
+      </c>
+      <c r="F2870" t="n">
+        <v>75.00700378417969</v>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B2871" t="n">
+        <v>4489.10009765625</v>
+      </c>
+      <c r="C2871" t="n">
+        <v>6.649499893188477</v>
+      </c>
+      <c r="D2871" t="n">
+        <v>1373.099975585938</v>
+      </c>
+      <c r="E2871" t="n">
+        <v>1937.400024414062</v>
+      </c>
+      <c r="F2871" t="n">
+        <v>75.31099700927734</v>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B2872" t="n">
+        <v>4436.7001953125</v>
+      </c>
+      <c r="C2872" t="n">
+        <v>6.480999946594238</v>
+      </c>
+      <c r="D2872" t="n">
+        <v>1317.099975585938</v>
+      </c>
+      <c r="E2872" t="n">
+        <v>1868.699951171875</v>
+      </c>
+      <c r="F2872" t="n">
+        <v>73.47599792480469</v>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B2873" t="n">
+        <v>4475.7998046875</v>
+      </c>
+      <c r="C2873" t="n">
+        <v>6.511000156402588</v>
+      </c>
+      <c r="D2873" t="n">
+        <v>1318.800048828125</v>
+      </c>
+      <c r="E2873" t="n">
+        <v>1894</v>
+      </c>
+      <c r="F2873" t="n">
+        <v>73.77899932861328</v>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B2874" t="n">
+        <v>4337.10009765625</v>
+      </c>
+      <c r="C2874" t="n">
+        <v>6.263500213623047</v>
+      </c>
+      <c r="D2874" t="n">
+        <v>1247.099975585938</v>
+      </c>
+      <c r="E2874" t="n">
+        <v>1792</v>
+      </c>
+      <c r="F2874" t="n">
+        <v>68.94300079345703</v>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B2875" t="n">
+        <v>4335.89990234375</v>
+      </c>
+      <c r="C2875" t="n">
+        <v>6.329500198364258</v>
+      </c>
+      <c r="D2875" t="n">
+        <v>1200.900024414062</v>
+      </c>
+      <c r="E2875" t="n">
+        <v>1749.400024414062</v>
+      </c>
+      <c r="F2875" t="n">
+        <v>68.42500305175781</v>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B2876" t="n">
+        <v>4260</v>
+      </c>
+      <c r="C2876" t="n">
+        <v>6.302499771118164</v>
+      </c>
+      <c r="D2876" t="n">
+        <v>1213.599975585938</v>
+      </c>
+      <c r="E2876" t="n">
+        <v>1708.599975585938</v>
+      </c>
+      <c r="F2876" t="n">
+        <v>65.09400177001953</v>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B2877" t="n">
+        <v>4108.2001953125</v>
+      </c>
+      <c r="C2877" t="n">
+        <v>6.249000072479248</v>
+      </c>
+      <c r="D2877" t="n">
+        <v>1230.800048828125</v>
+      </c>
+      <c r="E2877" t="n">
+        <v>1688</v>
+      </c>
+      <c r="F2877" t="n">
+        <v>64.5989990234375</v>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B2878" t="n">
+        <v>4090.300048828125</v>
+      </c>
+      <c r="C2878" t="n">
+        <v>6.258999824523926</v>
+      </c>
+      <c r="D2878" t="n">
+        <v>1234.599975585938</v>
+      </c>
+      <c r="E2878" t="n">
+        <v>1662.599975585938</v>
+      </c>
+      <c r="F2878" t="n">
+        <v>63.8849983215332</v>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B2879" t="n">
+        <v>4215</v>
+      </c>
+      <c r="C2879" t="n">
+        <v>6.430500030517578</v>
+      </c>
+      <c r="D2879" t="n">
+        <v>1276.199951171875</v>
+      </c>
+      <c r="E2879" t="n">
+        <v>1709.199951171875</v>
+      </c>
+      <c r="F2879" t="n">
+        <v>67.85900115966797</v>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B2880" t="n">
+        <v>4328</v>
+      </c>
+      <c r="C2880" t="n">
+        <v>6.482500076293945</v>
+      </c>
+      <c r="D2880" t="n">
+        <v>1346.800048828125</v>
+      </c>
+      <c r="E2880" t="n">
+        <v>1770</v>
+      </c>
+      <c r="F2880" t="n">
+        <v>70.06600189208984</v>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B2881" t="n">
+        <v>4330.89990234375</v>
+      </c>
+      <c r="C2881" t="n">
+        <v>6.488999843597412</v>
+      </c>
+      <c r="D2881" t="n">
+        <v>1355.900024414062</v>
+      </c>
+      <c r="E2881" t="n">
+        <v>1812.099975585938</v>
+      </c>
+      <c r="F2881" t="n">
+        <v>69.89900207519531</v>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2882" t="n">
+        <v>4358.89990234375</v>
+      </c>
+      <c r="C2882" t="n">
+        <v>6.481500148773193</v>
+      </c>
+      <c r="D2882" t="n">
+        <v>1349.099975585938</v>
+      </c>
+      <c r="E2882" t="n">
+        <v>1790.699951171875</v>
+      </c>
+      <c r="F2882" t="n">
+        <v>70.69599914550781</v>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B2883" t="n">
+        <v>4224.10009765625</v>
+      </c>
+      <c r="C2883" t="n">
+        <v>6.374499797821045</v>
+      </c>
+      <c r="D2883" t="n">
+        <v>1274.5</v>
+      </c>
+      <c r="E2883" t="n">
+        <v>1705.199951171875</v>
+      </c>
+      <c r="F2883" t="n">
+        <v>66.25499725341797</v>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B2884" t="n">
+        <v>4181.89990234375</v>
+      </c>
+      <c r="C2884" t="n">
+        <v>6.356500148773193</v>
+      </c>
+      <c r="D2884" t="n">
+        <v>1257.099975585938</v>
+      </c>
+      <c r="E2884" t="n">
+        <v>1670.300048828125</v>
+      </c>
+      <c r="F2884" t="n">
+        <v>65.52700042724609</v>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B2885" t="n">
+        <v>4129.89990234375</v>
+      </c>
+      <c r="C2885" t="n">
+        <v>6.140999794006348</v>
+      </c>
+      <c r="D2885" t="n">
+        <v>1230.699951171875</v>
+      </c>
+      <c r="E2885" t="n">
+        <v>1660.900024414062</v>
+      </c>
+      <c r="F2885" t="n">
+        <v>62.02000045776367</v>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B2886" t="n">
+        <v>3990.300048828125</v>
+      </c>
+      <c r="C2886" t="n">
+        <v>5.942999839782715</v>
+      </c>
+      <c r="D2886" t="n">
+        <v>1161.300048828125</v>
+      </c>
+      <c r="E2886" t="n">
+        <v>1580.599975585938</v>
+      </c>
+      <c r="F2886" t="n">
+        <v>58.05199813842773</v>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B2887" t="n">
+        <v>4030.5</v>
+      </c>
+      <c r="C2887" t="n">
+        <v>6.070499897003174</v>
+      </c>
+      <c r="D2887" t="n">
+        <v>1180.199951171875</v>
+      </c>
+      <c r="E2887" t="n">
+        <v>1601.699951171875</v>
+      </c>
+      <c r="F2887" t="n">
+        <v>58.34799957275391</v>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B2888" t="n">
+        <v>4078.699951171875</v>
+      </c>
+      <c r="C2888" t="n">
+        <v>6.141499996185303</v>
+      </c>
+      <c r="D2888" t="n">
+        <v>1209</v>
+      </c>
+      <c r="E2888" t="n">
+        <v>1630.900024414062</v>
+      </c>
+      <c r="F2888" t="n">
+        <v>59.21699905395508</v>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2889" t="n">
+        <v>4022.300048828125</v>
+      </c>
+      <c r="C2889" t="n">
+        <v>6.097499847412109</v>
+      </c>
+      <c r="D2889" t="n">
+        <v>1210.400024414062</v>
+      </c>
+      <c r="E2889" t="n">
+        <v>1574.5</v>
+      </c>
+      <c r="F2889" t="n">
+        <v>58.17499923706055</v>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="A2890" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B2890" t="n">
+        <v>4022.89990234375</v>
+      </c>
+      <c r="C2890" t="n">
+        <v>6.192500114440918</v>
+      </c>
+      <c r="D2890" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E2890" t="n">
+        <v>1550.199951171875</v>
+      </c>
+      <c r="F2890" t="n">
+        <v>59.47700119018555</v>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="A2891" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2891" t="n">
+        <v>4068.300048828125</v>
+      </c>
+      <c r="C2891" t="n">
+        <v>6.123499870300293</v>
+      </c>
+      <c r="D2891" t="n">
+        <v>1212.800048828125</v>
+      </c>
+      <c r="E2891" t="n">
+        <v>1588.900024414062</v>
+      </c>
+      <c r="F2891" t="n">
+        <v>60.08499908447266</v>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B2892" t="n">
+        <v>4112.7001953125</v>
+      </c>
+      <c r="C2892" t="n">
+        <v>6.114500045776367</v>
+      </c>
+      <c r="D2892" t="n">
+        <v>1261.900024414062</v>
+      </c>
+      <c r="E2892" t="n">
+        <v>1616.599975585938</v>
+      </c>
+      <c r="F2892" t="n">
+        <v>60.64300155639648</v>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B2893" t="n">
+        <v>4155.10009765625</v>
+      </c>
+      <c r="C2893" t="n">
+        <v>6.177999973297119</v>
+      </c>
+      <c r="D2893" t="n">
+        <v>1260.400024414062</v>
+      </c>
+      <c r="E2893" t="n">
+        <v>1631.699951171875</v>
+      </c>
+      <c r="F2893" t="n">
+        <v>61.91999816894531</v>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B2894" t="n">
+        <v>4145.2998046875</v>
+      </c>
+      <c r="C2894" t="n">
+        <v>6.171500205993652</v>
+      </c>
+      <c r="D2894" t="n">
+        <v>1270.599975585938</v>
+      </c>
+      <c r="E2894" t="n">
+        <v>1651.199951171875</v>
+      </c>
+      <c r="F2894" t="n">
+        <v>60.93099975585938</v>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B2895" t="n">
+        <v>4070.89990234375</v>
+      </c>
+      <c r="C2895" t="n">
+        <v>6.054500102996826</v>
+      </c>
+      <c r="D2895" t="n">
+        <v>1213.400024414062</v>
+      </c>
+      <c r="E2895" t="n">
+        <v>1576.400024414062</v>
+      </c>
+      <c r="F2895" t="n">
+        <v>58.16400146484375</v>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B2896" t="n">
+        <v>4130.60009765625</v>
+      </c>
+      <c r="C2896" t="n">
+        <v>6.215000152587891</v>
+      </c>
+      <c r="D2896" t="n">
+        <v>1243.900024414062</v>
+      </c>
+      <c r="E2896" t="n">
+        <v>1618.800048828125</v>
+      </c>
+      <c r="F2896" t="n">
+        <v>60.37799835205078</v>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B2897" t="n">
+        <v>4104.10009765625</v>
+      </c>
+      <c r="C2897" t="n">
+        <v>6.233500003814697</v>
+      </c>
+      <c r="D2897" t="n">
+        <v>1266.300048828125</v>
+      </c>
+      <c r="E2897" t="n">
+        <v>1618.099975585938</v>
+      </c>
+      <c r="F2897" t="n">
+        <v>59.80899810791016</v>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B2898" t="n">
+        <v>3997</v>
+      </c>
+      <c r="C2898" t="n">
+        <v>6.232999801635742</v>
+      </c>
+      <c r="D2898" t="n">
+        <v>1242.699951171875</v>
+      </c>
+      <c r="E2898" t="n">
+        <v>1602.199951171875</v>
+      </c>
+      <c r="F2898" t="n">
+        <v>57.63399887084961</v>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="A2899" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B2899" t="n">
+        <v>4061.10009765625</v>
+      </c>
+      <c r="C2899" t="n">
+        <v>6.329999923706055</v>
+      </c>
+      <c r="D2899" t="n">
+        <v>1298.599975585938</v>
+      </c>
+      <c r="E2899" t="n">
+        <v>1631.5</v>
+      </c>
+      <c r="F2899" t="n">
+        <v>58.77199935913086</v>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B2900" t="n">
+        <v>4044</v>
+      </c>
+      <c r="C2900" t="n">
+        <v>6.293499946594238</v>
+      </c>
+      <c r="D2900" t="n">
+        <v>1283.199951171875</v>
+      </c>
+      <c r="E2900" t="n">
+        <v>1631.5</v>
+      </c>
+      <c r="F2900" t="n">
+        <v>57.11000061035156</v>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B2901" t="n">
+        <v>3985.60009765625</v>
+      </c>
+      <c r="C2901" t="n">
+        <v>6.296000003814697</v>
+      </c>
+      <c r="D2901" t="n">
+        <v>1263.5</v>
+      </c>
+      <c r="E2901" t="n">
+        <v>1635.699951171875</v>
+      </c>
+      <c r="F2901" t="n">
+        <v>55.89799880981445</v>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B2902" t="n">
+        <v>4012.699951171875</v>
+      </c>
+      <c r="C2902" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="D2902" t="n">
+        <v>1244</v>
+      </c>
+      <c r="E2902" t="n">
+        <v>1605.800048828125</v>
+      </c>
+      <c r="F2902" t="n">
+        <v>56.03799819946289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
